--- a/artfynd/A 32475-2023 artfynd.xlsx
+++ b/artfynd/A 32475-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32475-2023 artfynd.xlsx
+++ b/artfynd/A 32475-2023 artfynd.xlsx
@@ -1949,7 +1949,7 @@
         <v>120018836</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 32475-2023 artfynd.xlsx
+++ b/artfynd/A 32475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102634895</v>
+        <v>112884894</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höksberget, Jmt</t>
+          <t>Stockselet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553311.6326737194</v>
+        <v>553296</v>
       </c>
       <c r="R2" t="n">
-        <v>7017521.187558858</v>
+        <v>7017506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,38 +754,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112884912</v>
+        <v>102634870</v>
       </c>
       <c r="B3" t="n">
-        <v>78021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,34 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stockselet, Jmt</t>
+          <t>Höksberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553306</v>
+        <v>553276</v>
       </c>
       <c r="R3" t="n">
-        <v>7017699</v>
+        <v>7017570</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,95 +858,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112884908</v>
+        <v>102634881</v>
       </c>
       <c r="B4" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stockselet, Jmt</t>
+          <t>Höksberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553392</v>
+        <v>553281</v>
       </c>
       <c r="R4" t="n">
-        <v>7017743</v>
+        <v>7017557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,59 +963,55 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112884913</v>
+        <v>112884900</v>
       </c>
       <c r="B5" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553306</v>
+        <v>553277</v>
       </c>
       <c r="R5" t="n">
-        <v>7017699</v>
+        <v>7017556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,37 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112884890</v>
+        <v>112884920</v>
       </c>
       <c r="B6" t="n">
-        <v>77424</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553279</v>
+        <v>553311</v>
       </c>
       <c r="R6" t="n">
-        <v>7017688</v>
+        <v>7017492</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,37 +1188,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112884909</v>
+        <v>112884922</v>
       </c>
       <c r="B7" t="n">
-        <v>79118</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553367</v>
+        <v>553280</v>
       </c>
       <c r="R7" t="n">
-        <v>7017727</v>
+        <v>7017531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,21 +1269,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1373,37 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112884910</v>
+        <v>112884927</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553367</v>
+        <v>553300</v>
       </c>
       <c r="R8" t="n">
-        <v>7017727</v>
+        <v>7017497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,21 +1370,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,15 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112884902</v>
+        <v>102634895</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,34 +1401,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockselet, Jmt</t>
+          <t>Höksberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553391</v>
+        <v>553312</v>
       </c>
       <c r="R9" t="n">
-        <v>7017747</v>
+        <v>7017521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,12 +1458,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,74 +1472,55 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112884884</v>
+        <v>112884916</v>
       </c>
       <c r="B10" t="n">
-        <v>91217</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1655,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553292</v>
+        <v>553281</v>
       </c>
       <c r="R10" t="n">
-        <v>7017694</v>
+        <v>7017529</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1721,15 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112884885</v>
+        <v>112884924</v>
       </c>
       <c r="B11" t="n">
-        <v>56753</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,42 +1607,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stockselet, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553394</v>
+        <v>553325</v>
       </c>
       <c r="R11" t="n">
-        <v>7017731</v>
+        <v>7017461</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,11 +1667,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,15 +1697,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112884926</v>
+        <v>112884884</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,21 +1708,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553271</v>
+        <v>553291</v>
       </c>
       <c r="R12" t="n">
-        <v>7017653</v>
+        <v>7017694</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,15 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120018836</v>
+        <v>112884925</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,34 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>stockselet, Jmt</t>
+          <t>Stockselet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553337</v>
+        <v>553325</v>
       </c>
       <c r="R13" t="n">
-        <v>7017713</v>
+        <v>7017461</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,12 +1863,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,17 +1883,1340 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112884898</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553271</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7017653</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112884912</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>553305</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7017699</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120018836</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>553337</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7017713</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Ulrika Westling</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY16" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112884890</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553278</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7017688</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112884902</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>553391</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7017747</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112884910</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>553367</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7017727</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128800688</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bygget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>553358</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017735</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128800689</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bygget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>553353</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7017743</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112884909</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>553367</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7017727</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>112884885</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>553394</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017731</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>112884908</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>553392</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7017743</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>112884913</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stockselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>553305</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7017699</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 32475-2023 artfynd.xlsx
+++ b/artfynd/A 32475-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884894</t>
         </is>
       </c>
     </row>
@@ -878,6 +888,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634870</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884900</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884922</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1385,6 +1420,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884927</t>
         </is>
       </c>
     </row>
@@ -1492,6 +1532,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102634895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884916</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884924</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884884</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884925</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884898</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2214,6 +2289,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120018836</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884890</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884902</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884910</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2658,6 +2753,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800688</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2769,6 +2869,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128800689</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2885,6 +2990,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884909</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2999,6 +3109,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884885</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3113,6 +3228,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884908</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3219,8 +3339,39 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112884913</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>